--- a/서버정보/20260706_리소스배포_개발.xlsx
+++ b/서버정보/20260706_리소스배포_개발.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99F9EF77-258E-4F13-812D-022793A7BFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1989C23B-0DCA-44A7-83BD-5CD39EBC70E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -2227,7 +2227,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2356,9 +2356,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8824,6 +8821,7 @@
       <c r="AF53" s="1"/>
     </row>
     <row r="54" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A54" s="42"/>
       <c r="B54" s="1" t="s">
         <v>31</v>
       </c>
@@ -8831,7 +8829,7 @@
         <f t="array" ref="C54">UPPER(INDEX(_xlfn.TEXTSPLIT($D54, "-"), 3))</f>
         <v>COM</v>
       </c>
-      <c r="D54" s="43" t="s">
+      <c r="D54" s="1" t="s">
         <v>50</v>
       </c>
       <c r="E54" s="1" t="s">
@@ -8864,7 +8862,7 @@
       <c r="N54" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="O54" s="43" t="str">
+      <c r="O54" s="1" t="str">
         <f>SUBSTITUTE(F54,"hazr-","")&amp;"-osdisk"</f>
         <v>d-com-scmsol01-osdisk</v>
       </c>
@@ -8874,10 +8872,10 @@
       <c r="Q54" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="R54" s="43"/>
+      <c r="R54" s="1"/>
       <c r="S54" s="1"/>
-      <c r="T54" s="43"/>
-      <c r="U54" s="43" t="str">
+      <c r="T54" s="1"/>
+      <c r="U54" s="1" t="str">
         <f>SUBSTITUTE(F54,"hazr-","")&amp;"-nic"</f>
         <v>d-com-scmsol01-nic</v>
       </c>
@@ -11856,6 +11854,7 @@
       <c r="R53" s="17"/>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A54" s="42"/>
       <c r="B54" s="16" t="s">
         <v>31</v>
       </c>
@@ -14546,6 +14545,7 @@
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A71" s="38"/>
       <c r="B71" s="36" t="s">
         <v>31</v>
       </c>
@@ -14601,6 +14601,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -14744,15 +14753,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
@@ -14770,6 +14770,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -14785,12 +14793,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>